--- a/Project_ETF/ETF_Investment_Portfolio/00929/ETF_Investment_Portfolio_20260612.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/00929/ETF_Investment_Portfolio_20260612.xlsx
@@ -616,7 +616,7 @@
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>12.95%</t>
+          <t>13.40%</t>
         </is>
       </c>
     </row>
@@ -638,7 +638,7 @@
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>10.12%</t>
+          <t>10.03%</t>
         </is>
       </c>
     </row>
@@ -660,7 +660,7 @@
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>6.60%</t>
+          <t>6.40%</t>
         </is>
       </c>
     </row>
@@ -682,7 +682,7 @@
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>5.62%</t>
+          <t>5.68%</t>
         </is>
       </c>
     </row>
@@ -704,7 +704,7 @@
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>5.60%</t>
+          <t>5.24%</t>
         </is>
       </c>
     </row>
@@ -726,7 +726,7 @@
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>4.40%</t>
+          <t>4.67%</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>3.62%</t>
+          <t>3.86%</t>
         </is>
       </c>
     </row>
@@ -770,7 +770,7 @@
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>2.97%</t>
+          <t>2.95%</t>
         </is>
       </c>
     </row>
@@ -792,183 +792,183 @@
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>2.94%</t>
+          <t>2.85%</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>3036</t>
+          <t>3260</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>文曄科技</t>
+          <t>威剛科技</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>15,276,000</t>
+          <t>8,758,000</t>
         </is>
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>2.71%</t>
+          <t>2.62%</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>3260</t>
+          <t>3036</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>威剛科技</t>
+          <t>文曄科技</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>8,758,000</t>
+          <t>15,276,000</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>2.63%</t>
+          <t>2.58%</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>5347</t>
+          <t>5536</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>世界先進</t>
+          <t>聖暉工程</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>19,558,000</t>
+          <t>2,827,000</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>2.41%</t>
+          <t>2.46%</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>3264</t>
+          <t>5347</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>欣銓科技</t>
+          <t>世界先進</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>14,334,000</t>
+          <t>19,558,000</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>2.35%</t>
+          <t>2.45%</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>2301</t>
+          <t>3264</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>光寶科技</t>
+          <t>欣銓科技</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>14,717,000</t>
+          <t>14,334,000</t>
         </is>
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>2.34%</t>
+          <t>2.41%</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>5536</t>
+          <t>2301</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>聖暉工程</t>
+          <t>光寶科技</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>2,827,000</t>
+          <t>14,717,000</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>2.32%</t>
+          <t>2.36%</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>2330</t>
+          <t>6257</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>台灣積體</t>
+          <t>矽格股份</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>1,101,000</t>
+          <t>12,063,000</t>
         </is>
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>1.89%</t>
+          <t>1.97%</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>6257</t>
+          <t>2330</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>矽格股份</t>
+          <t>台灣積體</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>12,063,000</t>
+          <t>1,101,000</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>1.89%</t>
+          <t>1.88%</t>
         </is>
       </c>
     </row>
@@ -990,95 +990,95 @@
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>1.84%</t>
+          <t>1.79%</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>2353</t>
+          <t>5483</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>宏碁股份</t>
+          <t>中美矽晶</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>61,597,000</t>
+          <t>14,856,000</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>1.73%</t>
+          <t>1.74%</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>4938</t>
+          <t>2353</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>和碩聯合</t>
+          <t>宏碁股份</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>23,608,000</t>
+          <t>61,597,000</t>
         </is>
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>1.72%</t>
+          <t>1.67%</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>3702</t>
+          <t>4938</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>大聯大控</t>
+          <t>和碩聯合</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>19,861,000</t>
+          <t>23,608,000</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>1.64%</t>
+          <t>1.62%</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>5483</t>
+          <t>3702</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>中美矽晶</t>
+          <t>大聯大控</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>14,856,000</t>
+          <t>19,861,000</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>1.64%</t>
+          <t>1.54%</t>
         </is>
       </c>
     </row>
@@ -1100,51 +1100,51 @@
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>1.38%</t>
+          <t>1.41%</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>6548</t>
+          <t>3090</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>長華科技</t>
+          <t>日電貿股</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>20,131,000</t>
+          <t>7,181,000</t>
         </is>
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>1.29%</t>
+          <t>1.36%</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>3090</t>
+          <t>6548</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>日電貿股</t>
+          <t>長華科技</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>7,181,000</t>
+          <t>20,131,000</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>1.28%</t>
+          <t>1.31%</t>
         </is>
       </c>
     </row>
@@ -1166,7 +1166,7 @@
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>1.20%</t>
+          <t>1.16%</t>
         </is>
       </c>
     </row>
@@ -1188,7 +1188,7 @@
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>1.17%</t>
+          <t>1.15%</t>
         </is>
       </c>
     </row>
@@ -1210,7 +1210,7 @@
       </c>
       <c r="D48" s="4" t="inlineStr">
         <is>
-          <t>1.15%</t>
+          <t>1.12%</t>
         </is>
       </c>
     </row>
@@ -1232,24 +1232,24 @@
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>1.05%</t>
+          <t>1.04%</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>2347</t>
+          <t>3680</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>聯強國際</t>
+          <t>家登精密</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>14,453,000</t>
+          <t>2,697,000</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
@@ -1261,66 +1261,66 @@
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>3680</t>
+          <t>3563</t>
         </is>
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>家登精密</t>
+          <t>牧德科技</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>2,697,000</t>
+          <t>1,868,000</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>0.99%</t>
+          <t>0.97%</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
         <is>
-          <t>3563</t>
+          <t>4966</t>
         </is>
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>牧德科技</t>
+          <t>譜瑞-KY</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>1,868,000</t>
+          <t>1,930,000</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr">
         <is>
-          <t>0.97%</t>
+          <t>0.96%</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="3" t="inlineStr">
         <is>
-          <t>4966</t>
+          <t>2347</t>
         </is>
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t>譜瑞-KY</t>
+          <t>聯強國際</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>1,930,000</t>
+          <t>14,453,000</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr">
         <is>
-          <t>0.97%</t>
+          <t>0.95%</t>
         </is>
       </c>
     </row>
@@ -1342,7 +1342,7 @@
       </c>
       <c r="D54" s="4" t="inlineStr">
         <is>
-          <t>0.71%</t>
+          <t>0.70%</t>
         </is>
       </c>
     </row>
@@ -1359,7 +1359,7 @@
       </c>
       <c r="C55" s="4" t="inlineStr">
         <is>
-          <t>861,416,462</t>
+          <t>893,352,462</t>
         </is>
       </c>
       <c r="D55" s="4" t="inlineStr">
@@ -1386,7 +1386,7 @@
       </c>
       <c r="D56" s="4" t="inlineStr">
         <is>
-          <t>0.66%</t>
+          <t>0.63%</t>
         </is>
       </c>
     </row>
@@ -1408,51 +1408,51 @@
       </c>
       <c r="D57" s="4" t="inlineStr">
         <is>
-          <t>0.55%</t>
+          <t>0.53%</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="3" t="inlineStr">
         <is>
-          <t>3005</t>
+          <t>6278</t>
         </is>
       </c>
       <c r="B58" s="3" t="inlineStr">
         <is>
-          <t>神基控股</t>
+          <t>台灣表面</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr">
         <is>
-          <t>6,222,000</t>
+          <t>3,412,000</t>
         </is>
       </c>
       <c r="D58" s="4" t="inlineStr">
         <is>
-          <t>0.50%</t>
+          <t>0.53%</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="3" t="inlineStr">
         <is>
-          <t>6278</t>
+          <t>3005</t>
         </is>
       </c>
       <c r="B59" s="3" t="inlineStr">
         <is>
-          <t>台灣表面</t>
+          <t>神基控股</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>3,412,000</t>
+          <t>6,222,000</t>
         </is>
       </c>
       <c r="D59" s="4" t="inlineStr">
         <is>
-          <t>0.50%</t>
+          <t>0.49%</t>
         </is>
       </c>
     </row>
@@ -1496,7 +1496,7 @@
       </c>
       <c r="D61" s="4" t="inlineStr">
         <is>
-          <t>0.45%</t>
+          <t>0.44%</t>
         </is>
       </c>
     </row>
@@ -1518,7 +1518,7 @@
       </c>
       <c r="D62" s="4" t="inlineStr">
         <is>
-          <t>0.43%</t>
+          <t>0.42%</t>
         </is>
       </c>
     </row>
@@ -1540,7 +1540,7 @@
       </c>
       <c r="D63" s="4" t="inlineStr">
         <is>
-          <t>0.40%</t>
+          <t>0.38%</t>
         </is>
       </c>
     </row>
@@ -1562,7 +1562,7 @@
       </c>
       <c r="D64" s="4" t="inlineStr">
         <is>
-          <t>0.33%</t>
+          <t>0.32%</t>
         </is>
       </c>
     </row>
@@ -1584,7 +1584,7 @@
       </c>
       <c r="D65" s="4" t="inlineStr">
         <is>
-          <t>0.31%</t>
+          <t>0.29%</t>
         </is>
       </c>
     </row>
@@ -1606,51 +1606,51 @@
       </c>
       <c r="D66" s="4" t="inlineStr">
         <is>
-          <t>0.28%</t>
+          <t>0.27%</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="3" t="inlineStr">
         <is>
-          <t>8454</t>
+          <t>2393</t>
         </is>
       </c>
       <c r="B67" s="3" t="inlineStr">
         <is>
-          <t>富邦媒體</t>
+          <t>億光電子</t>
         </is>
       </c>
       <c r="C67" s="4" t="inlineStr">
         <is>
-          <t>770,000</t>
+          <t>4,092,000</t>
         </is>
       </c>
       <c r="D67" s="4" t="inlineStr">
         <is>
-          <t>0.23%</t>
+          <t>0.21%</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="3" t="inlineStr">
         <is>
-          <t>2393</t>
+          <t>8454</t>
         </is>
       </c>
       <c r="B68" s="3" t="inlineStr">
         <is>
-          <t>億光電子</t>
+          <t>富邦媒體</t>
         </is>
       </c>
       <c r="C68" s="4" t="inlineStr">
         <is>
-          <t>4,092,000</t>
+          <t>770,000</t>
         </is>
       </c>
       <c r="D68" s="4" t="inlineStr">
         <is>
-          <t>0.21%</t>
+          <t>0.20%</t>
         </is>
       </c>
     </row>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="D70" s="4" t="inlineStr">
         <is>
-          <t>0.16%</t>
+          <t>0.15%</t>
         </is>
       </c>
     </row>
@@ -1777,12 +1777,12 @@
       </c>
       <c r="C74" s="4" t="inlineStr">
         <is>
-          <t>-42,161,253</t>
+          <t>-218,837,757</t>
         </is>
       </c>
       <c r="D74" s="4" t="inlineStr">
         <is>
-          <t>-0.03%</t>
+          <t>-0.16%</t>
         </is>
       </c>
     </row>
